--- a/naver-place-crawler/results_nail/세종_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/세종_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>발데렐라 \u002F\u002F 내성발톱 무좀발톱 발각질</t>
+          <t>도도네일 세종</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>iks9389@naver.com</t>
+          <t>dutjdgml70@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1391-4148</t>
+          <t>0507-1419-2052</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>세종 나성로 125-4 NS타워2. 806호</t>
+          <t>세종 보듬3로 92 해피라움 2동 2층 208호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaenpedi</t>
+          <t>https://https//www.instagram.com/s/aGlnaGxpZ2h0OjE3ODUwOTQ0NzAxNzkwMTI4?igshid=ZHpiMmlzc2NiZG9x</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vh7n</t>
+          <t>https://talk.naver.com/ct/wc5h5t</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>181</v>
+        <v>954</v>
       </c>
       <c r="Q2" t="n">
-        <v>327</v>
+        <v>796</v>
       </c>
       <c r="R2" t="n">
-        <v>508</v>
+        <v>1750</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1782711082</t>
+          <t>35559845</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782711082</t>
+          <t>https://m.place.naver.com/place/35559845</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>qkql7085@naver.com</t>
+          <t>woniovehotwo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>도도네일 세종</t>
+          <t>아실리네일 레푸스 세종종촌점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dutjdgml70@naver.com</t>
+          <t>ihiuisihi2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1419-2052</t>
+          <t>0507-1437-0204</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 보듬3로 92 해피라움 2동 2층 208호</t>
+          <t>세종 도움1로 106 메가시티 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://https//www.instagram.com/s/aGlnaGxpZ2h0OjE3ODUwOTQ0NzAxNzkwMTI4?igshid=ZHpiMmlzc2NiZG9x</t>
+          <t>https://blog.naver.com/ihiuisihi2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc5h5t</t>
+          <t>https://talk.naver.com/ct/wc4r67</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>948</v>
+        <v>1365</v>
       </c>
       <c r="Q4" t="n">
-        <v>791</v>
+        <v>89</v>
       </c>
       <c r="R4" t="n">
-        <v>1739</v>
+        <v>1454</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35559845</t>
+          <t>278347669</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35559845</t>
+          <t>https://m.place.naver.com/place/278347669</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>살롱드 토리네일</t>
+          <t>발데렐라 \u002F\u002F 내성발톱 무좀발톱 발각질</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ehdgml320@naver.com</t>
+          <t>go12174@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1337-9987</t>
+          <t>0507-1391-4148</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>세종 나성북1로 22 디펠리체 302호</t>
+          <t>세종 나성로 125-4 NS타워2. 806호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://instagram.com/salon_de_tory</t>
+          <t>https://www.instagram.com/chaenpedi</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tbr2</t>
+          <t>https://talk.naver.com/ct/w5vh7n</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>409</v>
+        <v>182</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="R5" t="n">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1533229640</t>
+          <t>1782711082</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533229640</t>
+          <t>https://m.place.naver.com/place/1782711082</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>포쉬네일 홈플러스세종점</t>
+          <t>살롱드 토리네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>licsyil@naver.com</t>
+          <t>seuggi7@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1429-4142</t>
+          <t>0507-1337-9987</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 절재로 154 홈플러스 세종점 1층</t>
+          <t>세종 나성북1로 22 디펠리체 302호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forsynail_sejong/</t>
+          <t>http://instagram.com/salon_de_tory</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wize</t>
+          <t>https://talk.naver.com/ct/w4tbr2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>308</v>
+        <v>410</v>
       </c>
       <c r="Q6" t="n">
-        <v>168</v>
+        <v>45</v>
       </c>
       <c r="R6" t="n">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1646553170</t>
+          <t>1533229640</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1646553170</t>
+          <t>https://m.place.naver.com/place/1533229640</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>세종뷰티포레</t>
+          <t>유리네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sejong_beautyforet@naver.com</t>
+          <t>sfsf0525@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1444-2049</t>
+          <t>0507-1349-4831</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 나성북로 21 센트럴타워 307호</t>
+          <t>세종 나성북로 30 어반아트리움퍼스트원 B동 2층 252호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sejong_beautyforet</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7oqq3p</t>
+          <t>https://talk.naver.com/ct/w4sut4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>142</v>
+        <v>204</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="R7" t="n">
-        <v>157</v>
+        <v>257</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2087005711</t>
+          <t>1257333138</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087005711</t>
+          <t>https://m.place.naver.com/place/1257333138</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>travelmaker86@naver.com</t>
+          <t>baby112@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="Q8" t="n">
         <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1250,39 +1250,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유리네일</t>
+          <t>온도뷰티&amp;오로지푸스 세종도담점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sfsf0525@naver.com</t>
+          <t>asdfgghd@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-4831</t>
+          <t>0507-1392-2270</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 나성북로 30 어반아트리움퍼스트원 B동 2층 252호</t>
+          <t>세종 보듬3로 8-13 황금빌딩 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xfxnWQb</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1297,27 +1297,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sut4</t>
+          <t>https://talk.naver.com/ct/w4c570</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="Q9" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1257333138</t>
+          <t>1038282578</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257333138</t>
+          <t>https://m.place.naver.com/place/1038282578</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sunnymoon715@naver.com</t>
+          <t>bmbk0206@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1544,39 +1544,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>세종뷰티앤네일</t>
+          <t>틴네일스튜디오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>guri7943@naver.com</t>
+          <t>ballcat@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1363-4557</t>
+          <t>0507-1306-0634</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>세종 갈매로 351 B동 3113-1호</t>
+          <t>세종 한누리대로 2236 판매시설-2동 2층 비212호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_SgqdX</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1592,22 +1592,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2071263488</t>
+          <t>2044417277</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2071263488</t>
+          <t>https://m.place.naver.com/place/2044417277</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1638,29 +1638,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>틴네일스튜디오</t>
+          <t>세종뷰티앤네일</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ballcat@naver.com</t>
+          <t>guri7943@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1306-0634</t>
+          <t>0507-1363-4557</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>세종 한누리대로 2236 판매시설-2동 2층 비212호</t>
+          <t>세종 갈매로 351 B동 3113-1호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tiin.naiilstudioo?igsh=MWc4bWNxN2o0NDU3ag==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1686,22 +1686,22 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1710,17 +1710,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2044417277</t>
+          <t>2071263488</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044417277</t>
+          <t>https://m.place.naver.com/place/2071263488</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/세종_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/세종_네일샵.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="Q2" t="n">
         <v>796</v>
       </c>
       <c r="R2" t="n">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일쏠 세종나성점</t>
+          <t>발데렐라 \u002F\u002F 내성발톱 무좀발톱 발각질</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>woniovehotwo@naver.com</t>
+          <t>go12174@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1444-0895</t>
+          <t>0507-1391-4148</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>세종 국세청로 45 상가 B동 2층 B214호</t>
+          <t>세종 나성로 125-4 NS타워2. 806호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__sol</t>
+          <t>https://www.instagram.com/chaenpedi</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/was1zm8</t>
+          <t>https://talk.naver.com/ct/w5vh7n</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>225</v>
+        <v>183</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>330</v>
       </c>
       <c r="R3" t="n">
-        <v>239</v>
+        <v>513</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2001571319</t>
+          <t>1782711082</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001571319</t>
+          <t>https://m.place.naver.com/place/1782711082</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아실리네일 레푸스 세종종촌점</t>
+          <t>헤이네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ihiuisihi2@naver.com</t>
+          <t>heynail_rim@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1437-0204</t>
+          <t>0507-1322-7878</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 메가시티 2층</t>
+          <t>세종 한누리대로 2200 단지내상가 B-109호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ihiuisihi2</t>
+          <t>http://instagram.com/hay_nail_brow</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc4r67</t>
+          <t>https://talk.naver.com/ct/w4mhbq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1365</v>
+        <v>182</v>
       </c>
       <c r="Q4" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="R4" t="n">
-        <v>1454</v>
+        <v>216</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>278347669</t>
+          <t>1211853649</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/278347669</t>
+          <t>https://m.place.naver.com/place/1211853649</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>발데렐라 \u002F\u002F 내성발톱 무좀발톱 발각질</t>
+          <t>아실리네일 레푸스 세종종촌점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>go12174@naver.com</t>
+          <t>ihiuisihi2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1391-4148</t>
+          <t>0507-1437-0204</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>세종 나성로 125-4 NS타워2. 806호</t>
+          <t>세종 도움1로 106 메가시티 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaenpedi</t>
+          <t>https://blog.naver.com/ihiuisihi2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vh7n</t>
+          <t>https://talk.naver.com/ct/wc4r67</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>182</v>
+        <v>1366</v>
       </c>
       <c r="Q5" t="n">
-        <v>330</v>
+        <v>89</v>
       </c>
       <c r="R5" t="n">
-        <v>512</v>
+        <v>1455</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1782711082</t>
+          <t>278347669</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782711082</t>
+          <t>https://m.place.naver.com/place/278347669</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>살롱드 토리네일</t>
+          <t>네일쏠 세종나성점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>seuggi7@naver.com</t>
+          <t>woniovehotwo@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1337-9987</t>
+          <t>0507-1444-0895</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 나성북1로 22 디펠리체 302호</t>
+          <t>세종 국세청로 45 상가 B동 2층 B214호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://instagram.com/salon_de_tory</t>
+          <t>https://www.instagram.com/nail__sol</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4tbr2</t>
+          <t>https://talk.naver.com/ct/was1zm8</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>410</v>
+        <v>230</v>
       </c>
       <c r="Q6" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>455</v>
+        <v>244</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1533229640</t>
+          <t>2001571319</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533229640</t>
+          <t>https://m.place.naver.com/place/2001571319</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>유리네일</t>
+          <t>세종뷰티포레</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sfsf0525@naver.com</t>
+          <t>sejong_beautyforet@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1349-4831</t>
+          <t>0507-1444-2049</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 나성북로 30 어반아트리움퍼스트원 B동 2층 252호</t>
+          <t>세종 나성북로 21 센트럴타워 307호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/sejong_beautyforet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sut4</t>
+          <t>https://talk.naver.com/ct/w7oqq3p</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="Q7" t="n">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="R7" t="n">
-        <v>257</v>
+        <v>180</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1257333138</t>
+          <t>2087005711</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257333138</t>
+          <t>https://m.place.naver.com/place/2087005711</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,34 +1250,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>온도뷰티&amp;오로지푸스 세종도담점</t>
+          <t>그린날</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>asdfgghd@naver.com</t>
+          <t>drawdays-m@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1392-2270</t>
+          <t>0507-1370-7075</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 보듬3로 8-13 황금빌딩 1층</t>
+          <t>세종 한누리대로 201 107호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xfxnWQb</t>
+          <t>https://www.instagram.com/draw_nail__/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4c570</t>
+          <t>https://talk.naver.com/ct/w48qml</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>186</v>
+        <v>751</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="R9" t="n">
-        <v>190</v>
+        <v>792</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1038282578</t>
+          <t>1731705891</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1038282578</t>
+          <t>https://m.place.naver.com/place/1731705891</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>다을네일</t>
+          <t>보뇌르네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bmbk0206@naver.com</t>
+          <t>yuna_ah@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1434-4802</t>
+          <t>0507-1327-8177</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>세종 소담3로 8 1동 4a호</t>
+          <t>세종 한누리대로 321 1층 149호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daeul_nail</t>
+          <t>https://www.instagram.com/bonheur_nail149?igsh=Y2Myd3YxbXVweXhz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wf2s2py</t>
+          <t>https://talk.naver.com/ct/w4il398</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2004641380</t>
+          <t>2023379775</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2004641380</t>
+          <t>https://m.place.naver.com/place/2023379775</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>보뇌르네일</t>
+          <t>다을네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>yuna_ah@naver.com</t>
+          <t>bmbk0206@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1327-8177</t>
+          <t>0507-1434-4802</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>세종 한누리대로 321 1층 149호</t>
+          <t>세종 소담3로 8 1동 4a호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonheur_nail149?igsh=Y2Myd3YxbXVweXhz&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/daeul_nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4il398</t>
+          <t>https://talk.naver.com/ct/wf2s2py</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2023379775</t>
+          <t>2004641380</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023379775</t>
+          <t>https://m.place.naver.com/place/2004641380</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ballcat@naver.com</t>
+          <t>hoonie917@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/세종_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/세종_네일샵.xlsx
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>발데렐라 \u002F\u002F 내성발톱 무좀발톱 발각질</t>
+          <t>네일쏠 세종나성점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>go12174@naver.com</t>
+          <t>woniovehotwo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1391-4148</t>
+          <t>0507-1444-0895</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>세종 나성로 125-4 NS타워2. 806호</t>
+          <t>세종 국세청로 45 상가 B동 2층 B214호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaenpedi</t>
+          <t>https://www.instagram.com/nail__sol</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5vh7n</t>
+          <t>https://talk.naver.com/ct/was1zm8</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="Q3" t="n">
-        <v>330</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>513</v>
+        <v>244</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1782711082</t>
+          <t>2001571319</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1782711082</t>
+          <t>https://m.place.naver.com/place/2001571319</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>헤이네일</t>
+          <t>발데렐라 \u002F\u002F 내성발톱 무좀발톱 발각질</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>heynail_rim@naver.com</t>
+          <t>go12174@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1322-7878</t>
+          <t>0507-1391-4148</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>세종 한누리대로 2200 단지내상가 B-109호</t>
+          <t>세종 나성로 125-4 NS타워2. 806호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/hay_nail_brow</t>
+          <t>https://www.instagram.com/chaenpedi</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4mhbq</t>
+          <t>https://talk.naver.com/ct/w5vh7n</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q4" t="n">
-        <v>34</v>
+        <v>330</v>
       </c>
       <c r="R4" t="n">
-        <v>216</v>
+        <v>513</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1211853649</t>
+          <t>1782711082</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1211853649</t>
+          <t>https://m.place.naver.com/place/1782711082</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아실리네일 레푸스 세종종촌점</t>
+          <t>헤이네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ihiuisihi2@naver.com</t>
+          <t>heynail_rim@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1437-0204</t>
+          <t>0507-1322-7878</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>세종 도움1로 106 메가시티 2층</t>
+          <t>세종 한누리대로 2200 단지내상가 B-109호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ihiuisihi2</t>
+          <t>http://instagram.com/hay_nail_brow</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wc4r67</t>
+          <t>https://talk.naver.com/ct/w4mhbq</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1366</v>
+        <v>182</v>
       </c>
       <c r="Q5" t="n">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="R5" t="n">
-        <v>1455</v>
+        <v>216</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>278347669</t>
+          <t>1211853649</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/278347669</t>
+          <t>https://m.place.naver.com/place/1211853649</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일쏠 세종나성점</t>
+          <t>네일바이피크닉</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>woniovehotwo@naver.com</t>
+          <t>ronnie53@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1444-0895</t>
+          <t>0507-1383-5476</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>세종 국세청로 45 상가 B동 2층 B214호</t>
+          <t>세종 한누리대로 321 3층 313호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__sol</t>
+          <t>https://www.instagram.com/nail.by.picnic/profilecard/?igsh=MW83cW0wamo5Zjc4bw==</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,14 +998,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/was1zm8</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>230</v>
+        <v>481</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R6" t="n">
-        <v>244</v>
+        <v>500</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2001571319</t>
+          <t>1483264148</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2001571319</t>
+          <t>https://m.place.naver.com/place/1483264148</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>세종뷰티포레</t>
+          <t>피어날, 네일 세종나성점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sejong_beautyforet@naver.com</t>
+          <t>aj5125@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1444-2049</t>
+          <t>0507-1434-2723</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 나성북로 21 센트럴타워 307호</t>
+          <t>세종 국세청로 45 상가동 2층 B202호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sejong_beautyforet</t>
+          <t>https://blog.naver.com/aj5125</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7oqq3p</t>
+          <t>https://talk.naver.com/ct/w5wz5i</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="R7" t="n">
-        <v>180</v>
+        <v>299</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2087005711</t>
+          <t>1092885867</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087005711</t>
+          <t>https://m.place.naver.com/place/1092885867</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>어라모드</t>
+          <t>세종뷰티포레</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>baby112@naver.com</t>
+          <t>sejong_beautyforet@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1330-6541</t>
+          <t>0507-1444-2049</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 한누리대로 2165 A동 136호 a la mode</t>
+          <t>세종 나성북로 21 센트럴타워 307호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___alamode_nail</t>
+          <t>https://www.instagram.com/sejong_beautyforet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45n06</t>
+          <t>https://talk.naver.com/ct/w7oqq3p</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>678</v>
+        <v>164</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R8" t="n">
-        <v>691</v>
+        <v>183</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1936290130</t>
+          <t>2087005711</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936290130</t>
+          <t>https://m.place.naver.com/place/2087005711</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>그린날</t>
+          <t>어라모드</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>drawdays-m@naver.com</t>
+          <t>baby112@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1370-7075</t>
+          <t>0507-1330-6541</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 한누리대로 201 107호</t>
+          <t>세종 한누리대로 2165 A동 136호 a la mode</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/draw_nail__/</t>
+          <t>https://www.instagram.com/___alamode_nail</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48qml</t>
+          <t>https://talk.naver.com/ct/w45n06</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>751</v>
+        <v>678</v>
       </c>
       <c r="Q9" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>792</v>
+        <v>691</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1731705891</t>
+          <t>1936290130</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1731705891</t>
+          <t>https://m.place.naver.com/place/1936290130</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1451,7 +1447,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bmbk0206@naver.com</t>
+          <t>sunnymoon715@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>

--- a/naver-place-crawler/results_nail/세종_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/세종_네일샵.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="37" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://https//www.instagram.com/s/aGlnaGxpZ2h0OjE3ODUwOTQ0NzAxNzkwMTI4?igshid=ZHpiMmlzc2NiZG9x</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="Q2" t="n">
         <v>796</v>
       </c>
       <c r="R2" t="n">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q3" t="n">
         <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>go12174@naver.com</t>
+          <t>vitajj@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaenpedi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q4" t="n">
         <v>330</v>
       </c>
       <c r="R4" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>heynail_rim@naver.com</t>
+          <t>naninuneno@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://instagram.com/hay_nail_brow</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.by.picnic/profilecard/?igsh=MW83cW0wamo5Zjc4bw==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피어날, 네일 세종나성점</t>
+          <t>세종뷰티포레</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>aj5125@naver.com</t>
+          <t>sejong_beautyforet@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1434-2723</t>
+          <t>0507-1444-2049</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>세종 국세청로 45 상가동 2층 B202호</t>
+          <t>세종 나성북로 21 센트럴타워 307호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aj5125</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wz5i</t>
+          <t>https://talk.naver.com/ct/w7oqq3p</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>256</v>
+        <v>166</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="R7" t="n">
-        <v>299</v>
+        <v>185</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1092885867</t>
+          <t>2087005711</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1092885867</t>
+          <t>https://m.place.naver.com/place/2087005711</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>세종뷰티포레</t>
+          <t>어라모드</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sejong_beautyforet@naver.com</t>
+          <t>baby112@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1444-2049</t>
+          <t>0507-1330-6541</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>세종 나성북로 21 센트럴타워 307호</t>
+          <t>세종 한누리대로 2165 A동 136호 a la mode</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sejong_beautyforet</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7oqq3p</t>
+          <t>https://talk.naver.com/ct/w45n06</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>164</v>
+        <v>678</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>183</v>
+        <v>691</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2087005711</t>
+          <t>1936290130</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087005711</t>
+          <t>https://m.place.naver.com/place/1936290130</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1246,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>어라모드</t>
+          <t>온도뷰티&amp;오로지푸스 세종도담점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>baby112@naver.com</t>
+          <t>asdfgghd@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1330-6541</t>
+          <t>0507-1392-2270</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>세종 한누리대로 2165 A동 136호 a la mode</t>
+          <t>세종 보듬3로 8-13 황금빌딩 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/___alamode_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45n06</t>
+          <t>https://talk.naver.com/ct/w4c570</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>678</v>
+        <v>188</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>691</v>
+        <v>192</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1936290130</t>
+          <t>1038282578</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1936290130</t>
+          <t>https://m.place.naver.com/place/1038282578</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonheur_nail149?igsh=Y2Myd3YxbXVweXhz&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daeul_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hoonie917@naver.com</t>
+          <t>aardeflower@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1562,17 +1562,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_SgqdX</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>guri7943@naver.com</t>
+          <t>silida51@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
